--- a/NUMEX_pre_RStudio/modelos_leafstr.xlsx
+++ b/NUMEX_pre_RStudio/modelos_leafstr.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="249">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">(Intercept)</t>
   </si>
   <si>
-    <t xml:space="preserve">SUBN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUBNP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUBP</t>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N × P</t>
   </si>
   <si>
     <t xml:space="preserve">SD (Intercept Bloque)</t>
@@ -119,18 +119,18 @@
     <t xml:space="preserve">(4.829)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.344)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-2.247</t>
   </si>
   <si>
     <t xml:space="preserve">(5.136)</t>
   </si>
   <si>
+    <t xml:space="preserve">3.538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.486)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.000</t>
   </si>
   <si>
@@ -161,18 +161,18 @@
     <t xml:space="preserve">(7.724)</t>
   </si>
   <si>
-    <t xml:space="preserve">14.369*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.867)</t>
-  </si>
-  <si>
     <t xml:space="preserve">7.687</t>
   </si>
   <si>
     <t xml:space="preserve">(5.135)</t>
   </si>
   <si>
+    <t xml:space="preserve">-17.815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9.798)</t>
+  </si>
+  <si>
     <t xml:space="preserve">7.217</t>
   </si>
   <si>
@@ -206,18 +206,18 @@
     <t xml:space="preserve">(1.793)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.847)</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.526</t>
   </si>
   <si>
     <t xml:space="preserve">(1.568)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.523)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.815</t>
   </si>
   <si>
@@ -248,18 +248,18 @@
     <t xml:space="preserve">(1.425)</t>
   </si>
   <si>
-    <t xml:space="preserve">-1.748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.324)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-2.550+</t>
   </si>
   <si>
     <t xml:space="preserve">(1.386)</t>
   </si>
   <si>
+    <t xml:space="preserve">3.544+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.020)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.163</t>
   </si>
   <si>
@@ -290,18 +290,18 @@
     <t xml:space="preserve">(6.954)</t>
   </si>
   <si>
-    <t xml:space="preserve">-2.907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8.387)</t>
-  </si>
-  <si>
     <t xml:space="preserve">7.024</t>
   </si>
   <si>
     <t xml:space="preserve">(6.725)</t>
   </si>
   <si>
+    <t xml:space="preserve">-1.918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10.544)</t>
+  </si>
+  <si>
     <t xml:space="preserve">11.484</t>
   </si>
   <si>
@@ -329,18 +329,18 @@
     <t xml:space="preserve">(4.255)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.629)</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.477</t>
   </si>
   <si>
     <t xml:space="preserve">(4.074)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.948)</t>
+  </si>
+  <si>
     <t xml:space="preserve">6.728</t>
   </si>
   <si>
@@ -365,13 +365,16 @@
     <t xml:space="preserve">(0.010)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.011</t>
+    <t xml:space="preserve">-0.001</t>
   </si>
   <si>
     <t xml:space="preserve">(0.011)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.001</t>
+    <t xml:space="preserve">-0.006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.016)</t>
   </si>
   <si>
     <t xml:space="preserve">0.024</t>
@@ -398,13 +401,16 @@
     <t xml:space="preserve">(0.006)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.008+</t>
+    <t xml:space="preserve">0.002</t>
   </si>
   <si>
     <t xml:space="preserve">(0.004)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.002</t>
+    <t xml:space="preserve">0.027*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.008)</t>
   </si>
   <si>
     <t xml:space="preserve">0.023</t>
@@ -437,24 +443,24 @@
     <t xml:space="preserve">(0.024)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.021)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.034)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.054</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.004</t>
   </si>
   <si>
-    <t xml:space="preserve">(0.025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.021)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.054</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.084</t>
   </si>
   <si>
@@ -473,10 +479,7 @@
     <t xml:space="preserve">(0.017)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.016)</t>
+    <t xml:space="preserve">-0.009</t>
   </si>
   <si>
     <t xml:space="preserve">0.042</t>
@@ -500,10 +503,7 @@
     <t xml:space="preserve">(0.023)</t>
   </si>
   <si>
-    <t xml:space="preserve">(0.028)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.009</t>
+    <t xml:space="preserve">(0.035)</t>
   </si>
   <si>
     <t xml:space="preserve">0.038</t>
@@ -527,12 +527,12 @@
     <t xml:space="preserve">-0.019</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.015</t>
-  </si>
-  <si>
     <t xml:space="preserve">(0.020)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.007</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.033</t>
   </si>
   <si>
@@ -557,126 +557,135 @@
     <t xml:space="preserve">(0.059)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.062)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.091)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-17.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toughness | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.083)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.153)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.101)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.188)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toughness | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.578***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.043)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.055)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.088)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-21.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toughness | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.488***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.045)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.094</t>
+  </si>
+  <si>
     <t xml:space="preserve">(0.065)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.062)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-17.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toughness | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.083)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.153)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.098)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.101)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toughness | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.578***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.043)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.064)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.055)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-21.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toughness | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.488***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.045)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.061)</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.064</t>
   </si>
   <si>
     <t xml:space="preserve">(0.063)</t>
   </si>
   <si>
+    <t xml:space="preserve">-0.146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.092)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.159</t>
   </si>
   <si>
@@ -698,18 +707,15 @@
     <t xml:space="preserve">(0.073)</t>
   </si>
   <si>
-    <t xml:space="preserve">(0.092)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.111)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-0.159+</t>
   </si>
   <si>
     <t xml:space="preserve">(0.089)</t>
   </si>
   <si>
+    <t xml:space="preserve">(0.139)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.055</t>
   </si>
   <si>
@@ -737,16 +743,16 @@
     <t xml:space="preserve">(0.053)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.071)</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.050</t>
   </si>
   <si>
     <t xml:space="preserve">(0.051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.087)</t>
   </si>
   <si>
     <t xml:space="preserve">0.093</t>
@@ -1442,7 +1448,7 @@
         <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
         <v>90</v>
@@ -1554,195 +1560,195 @@
         <v>119</v>
       </c>
       <c r="I10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J10" t="s">
         <v>39</v>
       </c>
       <c r="K10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L10" t="s">
         <v>41</v>
       </c>
       <c r="M10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N10" t="s">
         <v>29</v>
       </c>
       <c r="O10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L11" t="s">
         <v>55</v>
       </c>
       <c r="M11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H12" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="I12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s">
         <v>70</v>
       </c>
       <c r="M12" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="N12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s">
         <v>118</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F13" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="G13" t="s">
         <v>154</v>
       </c>
       <c r="H13" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="I13" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="J13" t="s">
         <v>39</v>
       </c>
       <c r="K13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L13" t="s">
         <v>84</v>
       </c>
       <c r="M13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N13" t="s">
         <v>29</v>
       </c>
       <c r="O13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C14" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F14" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="G14" t="s">
         <v>162</v>
       </c>
       <c r="H14" t="s">
+        <v>146</v>
+      </c>
+      <c r="I14" t="s">
         <v>163</v>
-      </c>
-      <c r="I14" t="s">
-        <v>161</v>
       </c>
       <c r="J14" t="s">
         <v>39</v>
@@ -1780,16 +1786,16 @@
         <v>144</v>
       </c>
       <c r="F15" t="s">
+        <v>161</v>
+      </c>
+      <c r="G15" t="s">
         <v>171</v>
       </c>
-      <c r="G15" t="s">
-        <v>162</v>
-      </c>
       <c r="H15" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="I15" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="J15" t="s">
         <v>39</v>
@@ -1827,269 +1833,269 @@
         <v>180</v>
       </c>
       <c r="F16" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J16" t="s">
         <v>39</v>
       </c>
       <c r="K16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s">
         <v>41</v>
       </c>
       <c r="M16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
       </c>
       <c r="O16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F17" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="G17" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H17" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I17" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J17" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K17" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L17" t="s">
         <v>55</v>
       </c>
       <c r="M17" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N17" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O17" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B18" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C18" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D18" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F18" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G18" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H18" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I18" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J18" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K18" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L18" t="s">
         <v>70</v>
       </c>
       <c r="M18" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N18" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="O18" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C19" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D19" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E19" t="s">
-        <v>181</v>
+        <v>219</v>
       </c>
       <c r="F19" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G19" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H19" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="I19" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J19" t="s">
         <v>206</v>
       </c>
       <c r="K19" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L19" t="s">
         <v>84</v>
       </c>
       <c r="M19" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="N19" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="O19" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C20" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D20" t="s">
         <v>71</v>
       </c>
       <c r="E20" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F20" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="G20" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H20" t="s">
-        <v>230</v>
+        <v>82</v>
       </c>
       <c r="I20" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J20" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K20" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L20" t="s">
         <v>97</v>
       </c>
       <c r="M20" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N20" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O20" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B21" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C21" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E21" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F21" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G21" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H21" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I21" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J21" t="s">
         <v>39</v>
       </c>
       <c r="K21" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L21" t="s">
         <v>110</v>
       </c>
       <c r="M21" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N21" t="s">
         <v>29</v>
       </c>
       <c r="O21" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
